--- a/시가총액TOP10.xlsx
+++ b/시가총액TOP10.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kqzx0\OneDrive\문서\UiPath\증권2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4364C693-B5C7-4613-A4AE-C12BA2A1189B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3D87FD6-99EA-44C8-92EA-9872FA2CE466}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2295" yWindow="2295" windowWidth="18300" windowHeight="11550" xr2:uid="{5C0FF506-DDBE-4CE9-A0E3-E4D7CC5A8EB7}"/>
+    <workbookView xWindow="2295" yWindow="2295" windowWidth="18300" windowHeight="11550" xr2:uid="{9BBDD86C-F59C-4373-BBB4-2FE28422A433}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -88,83 +88,83 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>코스피 5위</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>373220</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>LG에너지솔루션</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>코스피 6위</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>012450</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>한화에어로스페이스</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>코스피 7위</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>207940</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>삼성바이오로직스</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>코스피 8위</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>402340</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SK스퀘어</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>코스피 9위</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>034020</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>두산에너빌리티</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>코스피 10위</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>000270</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>기아</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>005380</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>현대차</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>코스피 5위</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>373220</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>LG에너지솔루션</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>코스피 6위</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>012450</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>한화에어로스페이스</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>코스피 7위</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>207940</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>삼성바이오로직스</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>코스피 8위</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>402340</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SK스퀘어</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>코스피 9위</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>034020</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>두산에너빌리티</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>코스피 10위</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>000270</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>기아</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -531,7 +531,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5BE23455-7BEE-4468-8106-CD2C94A367A8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{49F37D8D-84CB-4C14-B738-3AE3FFBD05D1}">
   <dimension ref="A1:C11"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
@@ -584,76 +584,76 @@
         <v>12</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="C6" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
+        <v>16</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" t="s">
         <v>18</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C7" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
+        <v>19</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C8" t="s">
         <v>21</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="C8" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
+        <v>22</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C9" t="s">
         <v>24</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="C9" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
+        <v>25</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C10" t="s">
         <v>27</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="C10" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
+        <v>28</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C11" t="s">
         <v>30</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="C11" t="s">
-        <v>32</v>
       </c>
     </row>
   </sheetData>
